--- a/pinn_for_hydraulic_transients/RU_PG/test.xlsx
+++ b/pinn_for_hydraulic_transients/RU_PG/test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\laaf-pinn-for-water-hammer\pinn_for_hydraulic_transients\RU_PG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\BeckhoffAds\laaf-pinn-for-water-hammer\pinn_for_hydraulic_transients\RU_PG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5812C90-8DAA-465F-80C4-57B124424ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF638D7-5DF0-49A3-AA23-0EED922A51CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{2B0B7EC7-0844-40D0-909A-C495F946D021}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2B0B7EC7-0844-40D0-909A-C495F946D021}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -73,13 +76,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -24124,8 +24130,8 @@
       <c r="A2157" s="2">
         <v>1379.3130000000001</v>
       </c>
-      <c r="B2157" s="1">
-        <v>9.9687499999999998E-2</v>
+      <c r="B2157" s="4">
+        <v>0.01</v>
       </c>
       <c r="C2157" s="2">
         <v>51.003909999999998</v>
@@ -24135,8 +24141,8 @@
       <c r="A2158" s="2">
         <v>1376.3130000000001</v>
       </c>
-      <c r="B2158" s="1">
-        <v>9.9699074074074079E-2</v>
+      <c r="B2158" s="4">
+        <v>0.02</v>
       </c>
       <c r="C2158" s="2">
         <v>51.003909999999998</v>
@@ -24146,8 +24152,8 @@
       <c r="A2159" s="2">
         <v>1380.0630000000001</v>
       </c>
-      <c r="B2159" s="1">
-        <v>9.9733796296296293E-2</v>
+      <c r="B2159" s="4">
+        <v>0.03</v>
       </c>
       <c r="C2159" s="2">
         <v>51.003909999999998</v>
@@ -24157,8 +24163,8 @@
       <c r="A2160" s="2">
         <v>1384.3130000000001</v>
       </c>
-      <c r="B2160" s="1">
-        <v>9.9745370370370373E-2</v>
+      <c r="B2160" s="4">
+        <v>0.04</v>
       </c>
       <c r="C2160" s="2">
         <v>51.003909999999998</v>
@@ -24168,8 +24174,8 @@
       <c r="A2161" s="2">
         <v>1374.8130000000001</v>
       </c>
-      <c r="B2161" s="1">
-        <v>9.9803240740740734E-2</v>
+      <c r="B2161" s="4">
+        <v>0.05</v>
       </c>
       <c r="C2161" s="2">
         <v>51.003909999999998</v>
@@ -24179,8 +24185,8 @@
       <c r="A2162" s="2">
         <v>1365.375</v>
       </c>
-      <c r="B2162" s="1">
-        <v>9.9814814814814815E-2</v>
+      <c r="B2162" s="4">
+        <v>0.06</v>
       </c>
       <c r="C2162" s="2">
         <v>51.003909999999998</v>
@@ -24190,8 +24196,8 @@
       <c r="A2163" s="2">
         <v>1362.5</v>
       </c>
-      <c r="B2163" s="1">
-        <v>9.9872685185185189E-2</v>
+      <c r="B2163" s="4">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C2163" s="2">
         <v>51.003909999999998</v>
@@ -24201,8 +24207,8 @@
       <c r="A2164" s="2">
         <v>1367.375</v>
       </c>
-      <c r="B2164" s="1">
-        <v>9.9918981481481484E-2</v>
+      <c r="B2164" s="4">
+        <v>0.08</v>
       </c>
       <c r="C2164" s="2">
         <v>51.003909999999998</v>
@@ -24212,8 +24218,8 @@
       <c r="A2165" s="2">
         <v>1364.5</v>
       </c>
-      <c r="B2165" s="1">
-        <v>9.9942129629629631E-2</v>
+      <c r="B2165" s="4">
+        <v>0.09</v>
       </c>
       <c r="C2165" s="2">
         <v>51.003909999999998</v>
@@ -24223,8 +24229,8 @@
       <c r="A2166" s="2">
         <v>1361.8130000000001</v>
       </c>
-      <c r="B2166" s="1">
-        <v>9.9953703703703697E-2</v>
+      <c r="B2166" s="4">
+        <v>0.1</v>
       </c>
       <c r="C2166" s="2">
         <v>51.003909999999998</v>
@@ -24234,8 +24240,8 @@
       <c r="A2167" s="2">
         <v>1364.5</v>
       </c>
-      <c r="B2167" s="1">
-        <v>0.1</v>
+      <c r="B2167" s="4">
+        <v>0.11</v>
       </c>
       <c r="C2167" s="2">
         <v>51.003909999999998</v>
@@ -24245,8 +24251,8 @@
       <c r="A2168" s="2">
         <v>1367.9380000000001</v>
       </c>
-      <c r="B2168" s="1">
-        <v>0.10001157407407407</v>
+      <c r="B2168" s="4">
+        <v>0.12</v>
       </c>
       <c r="C2168" s="2">
         <v>51.003909999999998</v>
@@ -24256,8 +24262,8 @@
       <c r="A2169" s="2">
         <v>1370.5630000000001</v>
       </c>
-      <c r="B2169" s="1">
-        <v>0.10002314814814815</v>
+      <c r="B2169" s="4">
+        <v>0.13</v>
       </c>
       <c r="C2169" s="2">
         <v>51.003909999999998</v>
@@ -24267,8 +24273,8 @@
       <c r="A2170" s="2">
         <v>1374.0630000000001</v>
       </c>
-      <c r="B2170" s="1">
-        <v>0.10003472222222222</v>
+      <c r="B2170" s="4">
+        <v>0.14000000000000001</v>
       </c>
       <c r="C2170" s="2">
         <v>51.003909999999998</v>
@@ -24278,8 +24284,8 @@
       <c r="A2171" s="2">
         <v>1376.6880000000001</v>
       </c>
-      <c r="B2171" s="1">
-        <v>0.10008101851851851</v>
+      <c r="B2171" s="4">
+        <v>0.15</v>
       </c>
       <c r="C2171" s="2">
         <v>51.003909999999998</v>
@@ -24289,8 +24295,8 @@
       <c r="A2172" s="2">
         <v>1373</v>
       </c>
-      <c r="B2172" s="1">
-        <v>0.10012731481481481</v>
+      <c r="B2172" s="4">
+        <v>0.16</v>
       </c>
       <c r="C2172" s="2">
         <v>51.003909999999998</v>
@@ -24300,8 +24306,8 @@
       <c r="A2173" s="2">
         <v>1375.8130000000001</v>
       </c>
-      <c r="B2173" s="1">
-        <v>0.10016203703703704</v>
+      <c r="B2173" s="4">
+        <v>0.17</v>
       </c>
       <c r="C2173" s="2">
         <v>51.003909999999998</v>
@@ -24311,8 +24317,8 @@
       <c r="A2174" s="2">
         <v>1371.875</v>
       </c>
-      <c r="B2174" s="1">
-        <v>0.10020833333333333</v>
+      <c r="B2174" s="4">
+        <v>0.18</v>
       </c>
       <c r="C2174" s="2">
         <v>51.003909999999998</v>
@@ -24322,8 +24328,8 @@
       <c r="A2175" s="2">
         <v>1369.6880000000001</v>
       </c>
-      <c r="B2175" s="1">
-        <v>0.10021990740740741</v>
+      <c r="B2175" s="4">
+        <v>0.19</v>
       </c>
       <c r="C2175" s="2">
         <v>51.003909999999998</v>
@@ -24333,8 +24339,8 @@
       <c r="A2176" s="2">
         <v>1366.5</v>
       </c>
-      <c r="B2176" s="1">
-        <v>0.10024305555555556</v>
+      <c r="B2176" s="4">
+        <v>0.2</v>
       </c>
       <c r="C2176" s="2">
         <v>51.003909999999998</v>
@@ -24344,8 +24350,8 @@
       <c r="A2177" s="2">
         <v>1357</v>
       </c>
-      <c r="B2177" s="1">
-        <v>0.10030092592592593</v>
+      <c r="B2177" s="4">
+        <v>0.21</v>
       </c>
       <c r="C2177" s="2">
         <v>51.003909999999998</v>
@@ -24355,8 +24361,8 @@
       <c r="A2178" s="2">
         <v>1353.25</v>
       </c>
-      <c r="B2178" s="1">
-        <v>0.1003125</v>
+      <c r="B2178" s="4">
+        <v>0.22</v>
       </c>
       <c r="C2178" s="2">
         <v>51.003909999999998</v>
@@ -24366,8 +24372,8 @@
       <c r="A2179" s="2">
         <v>1358.875</v>
       </c>
-      <c r="B2179" s="1">
-        <v>0.10032407407407408</v>
+      <c r="B2179" s="4">
+        <v>0.23</v>
       </c>
       <c r="C2179" s="2">
         <v>51.003909999999998</v>
@@ -24377,8 +24383,8 @@
       <c r="A2180" s="2">
         <v>1362.5</v>
       </c>
-      <c r="B2180" s="1">
-        <v>0.10033564814814815</v>
+      <c r="B2180" s="4">
+        <v>0.24</v>
       </c>
       <c r="C2180" s="2">
         <v>51.003909999999998</v>
@@ -24388,8 +24394,8 @@
       <c r="A2181" s="2">
         <v>1365.25</v>
       </c>
-      <c r="B2181" s="1">
-        <v>0.10034722222222223</v>
+      <c r="B2181" s="4">
+        <v>0.25</v>
       </c>
       <c r="C2181" s="2">
         <v>51.003909999999998</v>
@@ -24399,8 +24405,8 @@
       <c r="A2182" s="2">
         <v>1369.125</v>
       </c>
-      <c r="B2182" s="1">
-        <v>0.10035879629629629</v>
+      <c r="B2182" s="4">
+        <v>0.26</v>
       </c>
       <c r="C2182" s="2">
         <v>51.003909999999998</v>
@@ -24410,8 +24416,8 @@
       <c r="A2183" s="2">
         <v>1376.8130000000001</v>
       </c>
-      <c r="B2183" s="1">
-        <v>0.10037037037037037</v>
+      <c r="B2183" s="4">
+        <v>0.27</v>
       </c>
       <c r="C2183" s="2">
         <v>51.160159999999998</v>
@@ -24421,8 +24427,8 @@
       <c r="A2184" s="2">
         <v>1382.9380000000001</v>
       </c>
-      <c r="B2184" s="1">
-        <v>0.10038194444444444</v>
+      <c r="B2184" s="4">
+        <v>0.28000000000000003</v>
       </c>
       <c r="C2184" s="2">
         <v>51.160159999999998</v>
@@ -24432,8 +24438,8 @@
       <c r="A2185" s="2">
         <v>1388.5</v>
       </c>
-      <c r="B2185" s="1">
-        <v>0.10039351851851852</v>
+      <c r="B2185" s="4">
+        <v>0.28999999999999998</v>
       </c>
       <c r="C2185" s="2">
         <v>51.160159999999998</v>
@@ -24443,8 +24449,8 @@
       <c r="A2186" s="2">
         <v>1391.3130000000001</v>
       </c>
-      <c r="B2186" s="1">
-        <v>0.10040509259259259</v>
+      <c r="B2186" s="4">
+        <v>0.3</v>
       </c>
       <c r="C2186" s="2">
         <v>51.160159999999998</v>
@@ -24454,8 +24460,8 @@
       <c r="A2187" s="2">
         <v>1396.5630000000001</v>
       </c>
-      <c r="B2187" s="1">
-        <v>0.10046296296296296</v>
+      <c r="B2187" s="4">
+        <v>0.31</v>
       </c>
       <c r="C2187" s="2">
         <v>51.160159999999998</v>
@@ -24465,8 +24471,8 @@
       <c r="A2188" s="2">
         <v>1401.125</v>
       </c>
-      <c r="B2188" s="1">
-        <v>0.10047453703703704</v>
+      <c r="B2188" s="4">
+        <v>0.32</v>
       </c>
       <c r="C2188" s="2">
         <v>51.160159999999998</v>
@@ -24476,8 +24482,8 @@
       <c r="A2189" s="2">
         <v>1405.625</v>
       </c>
-      <c r="B2189" s="1">
-        <v>0.10048611111111111</v>
+      <c r="B2189" s="4">
+        <v>0.33</v>
       </c>
       <c r="C2189" s="2">
         <v>51.160159999999998</v>
@@ -24487,8 +24493,8 @@
       <c r="A2190" s="2">
         <v>1407.9380000000001</v>
       </c>
-      <c r="B2190" s="1">
-        <v>0.10049768518518519</v>
+      <c r="B2190" s="4">
+        <v>0.34</v>
       </c>
       <c r="C2190" s="2">
         <v>51.160159999999998</v>
@@ -24498,8 +24504,8 @@
       <c r="A2191" s="2">
         <v>1410</v>
       </c>
-      <c r="B2191" s="1">
-        <v>0.1005324074074074</v>
+      <c r="B2191" s="4">
+        <v>0.35</v>
       </c>
       <c r="C2191" s="2">
         <v>51.160159999999998</v>
@@ -24509,8 +24515,8 @@
       <c r="A2192" s="2">
         <v>1400.375</v>
       </c>
-      <c r="B2192" s="1">
-        <v>0.10054398148148148</v>
+      <c r="B2192" s="4">
+        <v>0.36</v>
       </c>
       <c r="C2192" s="2">
         <v>51.160159999999998</v>
@@ -24520,8 +24526,8 @@
       <c r="A2193" s="2">
         <v>1391.6880000000001</v>
       </c>
-      <c r="B2193" s="1">
-        <v>0.10055555555555555</v>
+      <c r="B2193" s="4">
+        <v>0.37</v>
       </c>
       <c r="C2193" s="2">
         <v>51.160159999999998</v>
@@ -24531,8 +24537,8 @@
       <c r="A2194" s="2">
         <v>1388.9380000000001</v>
       </c>
-      <c r="B2194" s="1">
-        <v>0.1005787037037037</v>
+      <c r="B2194" s="4">
+        <v>0.38</v>
       </c>
       <c r="C2194" s="2">
         <v>51.160159999999998</v>
@@ -24542,8 +24548,8 @@
       <c r="A2195" s="2">
         <v>1386.875</v>
       </c>
-      <c r="B2195" s="1">
-        <v>0.10059027777777778</v>
+      <c r="B2195" s="4">
+        <v>0.39</v>
       </c>
       <c r="C2195" s="2">
         <v>51.160159999999998</v>
@@ -24553,8 +24559,8 @@
       <c r="A2196" s="2">
         <v>1382.0630000000001</v>
       </c>
-      <c r="B2196" s="1">
-        <v>0.10061342592592593</v>
+      <c r="B2196" s="4">
+        <v>0.4</v>
       </c>
       <c r="C2196" s="2">
         <v>51.160159999999998</v>
@@ -24564,8 +24570,8 @@
       <c r="A2197" s="2">
         <v>1378.8130000000001</v>
       </c>
-      <c r="B2197" s="1">
-        <v>0.10063657407407407</v>
+      <c r="B2197" s="4">
+        <v>0.41</v>
       </c>
       <c r="C2197" s="2">
         <v>51.160159999999998</v>
@@ -24575,8 +24581,8 @@
       <c r="A2198" s="2">
         <v>1376.5</v>
       </c>
-      <c r="B2198" s="1">
-        <v>0.10065972222222222</v>
+      <c r="B2198" s="4">
+        <v>0.42</v>
       </c>
       <c r="C2198" s="2">
         <v>51.160159999999998</v>
@@ -24586,8 +24592,8 @@
       <c r="A2199" s="2">
         <v>1372.8130000000001</v>
       </c>
-      <c r="B2199" s="1">
-        <v>0.10068287037037037</v>
+      <c r="B2199" s="4">
+        <v>0.43</v>
       </c>
       <c r="C2199" s="2">
         <v>51.160159999999998</v>
@@ -24597,8 +24603,8 @@
       <c r="A2200" s="2">
         <v>1375.5</v>
       </c>
-      <c r="B2200" s="1">
-        <v>0.10070601851851851</v>
+      <c r="B2200" s="4">
+        <v>0.44</v>
       </c>
       <c r="C2200" s="2">
         <v>51.160159999999998</v>
@@ -24608,8 +24614,8 @@
       <c r="A2201" s="2">
         <v>1377.75</v>
       </c>
-      <c r="B2201" s="1">
-        <v>0.10074074074074074</v>
+      <c r="B2201" s="4">
+        <v>0.45</v>
       </c>
       <c r="C2201" s="2">
         <v>51.160159999999998</v>
@@ -24619,8 +24625,8 @@
       <c r="A2202" s="2">
         <v>1381.4380000000001</v>
       </c>
-      <c r="B2202" s="1">
-        <v>0.10075231481481481</v>
+      <c r="B2202" s="4">
+        <v>0.46</v>
       </c>
       <c r="C2202" s="2">
         <v>51.160159999999998</v>
@@ -24630,8 +24636,8 @@
       <c r="A2203" s="2">
         <v>1377.25</v>
       </c>
-      <c r="B2203" s="1">
-        <v>0.10079861111111112</v>
+      <c r="B2203" s="4">
+        <v>0.47</v>
       </c>
       <c r="C2203" s="2">
         <v>51.160159999999998</v>
@@ -24641,8 +24647,8 @@
       <c r="A2204" s="2">
         <v>1380.4380000000001</v>
       </c>
-      <c r="B2204" s="1">
-        <v>0.10082175925925926</v>
+      <c r="B2204" s="4">
+        <v>0.48</v>
       </c>
       <c r="C2204" s="2">
         <v>51.160159999999998</v>
@@ -24652,8 +24658,8 @@
       <c r="A2205" s="2">
         <v>1385.25</v>
       </c>
-      <c r="B2205" s="1">
-        <v>0.10087962962962962</v>
+      <c r="B2205" s="4">
+        <v>0.49</v>
       </c>
       <c r="C2205" s="2">
         <v>51.160159999999998</v>
@@ -24663,8 +24669,8 @@
       <c r="A2206" s="2">
         <v>1390</v>
       </c>
-      <c r="B2206" s="1">
-        <v>0.10089120370370371</v>
+      <c r="B2206" s="4">
+        <v>0.5</v>
       </c>
       <c r="C2206" s="2">
         <v>51.160159999999998</v>
@@ -24674,8 +24680,8 @@
       <c r="A2207" s="2">
         <v>1386.3130000000001</v>
       </c>
-      <c r="B2207" s="1">
-        <v>0.10091435185185185</v>
+      <c r="B2207" s="4">
+        <v>0.51</v>
       </c>
       <c r="C2207" s="2">
         <v>51.160159999999998</v>
@@ -24685,8 +24691,8 @@
       <c r="A2208" s="2">
         <v>1388.5630000000001</v>
       </c>
-      <c r="B2208" s="1">
-        <v>0.1009375</v>
+      <c r="B2208" s="4">
+        <v>0.52</v>
       </c>
       <c r="C2208" s="2">
         <v>51.160159999999998</v>
@@ -24696,8 +24702,8 @@
       <c r="A2209" s="2">
         <v>1390.875</v>
       </c>
-      <c r="B2209" s="1">
-        <v>0.10101851851851852</v>
+      <c r="B2209" s="4">
+        <v>0.53</v>
       </c>
       <c r="C2209" s="2">
         <v>51.160159999999998</v>
@@ -24707,8 +24713,8 @@
       <c r="A2210" s="2">
         <v>1395</v>
       </c>
-      <c r="B2210" s="1">
-        <v>0.10108796296296296</v>
+      <c r="B2210" s="4">
+        <v>0.54</v>
       </c>
       <c r="C2210" s="2">
         <v>51.160159999999998</v>
@@ -24718,8 +24724,8 @@
       <c r="A2211" s="2">
         <v>1388.625</v>
       </c>
-      <c r="B2211" s="1">
-        <v>0.10111111111111111</v>
+      <c r="B2211" s="4">
+        <v>0.55000000000000004</v>
       </c>
       <c r="C2211" s="2">
         <v>51.160159999999998</v>
@@ -24729,8 +24735,8 @@
       <c r="A2212" s="2">
         <v>1392.75</v>
       </c>
-      <c r="B2212" s="1">
-        <v>0.10113425925925926</v>
+      <c r="B2212" s="4">
+        <v>0.56000000000000005</v>
       </c>
       <c r="C2212" s="2">
         <v>51.160159999999998</v>
@@ -24740,8 +24746,8 @@
       <c r="A2213" s="2">
         <v>1394.875</v>
       </c>
-      <c r="B2213" s="1">
-        <v>0.10114583333333334</v>
+      <c r="B2213" s="4">
+        <v>0.56999999999999995</v>
       </c>
       <c r="C2213" s="2">
         <v>51.160159999999998</v>
@@ -24751,8 +24757,8 @@
       <c r="A2214" s="2">
         <v>1397.375</v>
       </c>
-      <c r="B2214" s="1">
-        <v>0.10118055555555555</v>
+      <c r="B2214" s="4">
+        <v>0.57999999999999996</v>
       </c>
       <c r="C2214" s="2">
         <v>51.160159999999998</v>
@@ -24762,8 +24768,8 @@
       <c r="A2215" s="2">
         <v>1394.5630000000001</v>
       </c>
-      <c r="B2215" s="1">
-        <v>0.10119212962962963</v>
+      <c r="B2215" s="4">
+        <v>0.59</v>
       </c>
       <c r="C2215" s="2">
         <v>51.160159999999998</v>
@@ -24773,8 +24779,8 @@
       <c r="A2216" s="2">
         <v>1391.625</v>
       </c>
-      <c r="B2216" s="1">
-        <v>0.1012037037037037</v>
+      <c r="B2216" s="4">
+        <v>0.6</v>
       </c>
       <c r="C2216" s="2">
         <v>51.160159999999998</v>
@@ -24784,8 +24790,8 @@
       <c r="A2217" s="2">
         <v>1394.625</v>
       </c>
-      <c r="B2217" s="1">
-        <v>0.10125000000000001</v>
+      <c r="B2217" s="4">
+        <v>0.61</v>
       </c>
       <c r="C2217" s="2">
         <v>51.160159999999998</v>
@@ -24795,8 +24801,8 @@
       <c r="A2218" s="2">
         <v>1392.5</v>
       </c>
-      <c r="B2218" s="1">
-        <v>0.10126157407407407</v>
+      <c r="B2218" s="4">
+        <v>0.62</v>
       </c>
       <c r="C2218" s="2">
         <v>51.160159999999998</v>
@@ -24806,8 +24812,8 @@
       <c r="A2219" s="2">
         <v>1390.3130000000001</v>
       </c>
-      <c r="B2219" s="1">
-        <v>0.10127314814814815</v>
+      <c r="B2219" s="4">
+        <v>0.63</v>
       </c>
       <c r="C2219" s="2">
         <v>51.160159999999998</v>
@@ -24817,8 +24823,8 @@
       <c r="A2220" s="2">
         <v>1394.25</v>
       </c>
-      <c r="B2220" s="1">
-        <v>0.10133101851851851</v>
+      <c r="B2220" s="4">
+        <v>0.64</v>
       </c>
       <c r="C2220" s="2">
         <v>51.160159999999998</v>
@@ -24828,8 +24834,8 @@
       <c r="A2221" s="2">
         <v>1396.3130000000001</v>
       </c>
-      <c r="B2221" s="1">
-        <v>0.1013425925925926</v>
+      <c r="B2221" s="4">
+        <v>0.65</v>
       </c>
       <c r="C2221" s="2">
         <v>51.160159999999998</v>
@@ -24839,8 +24845,8 @@
       <c r="A2222" s="2">
         <v>1398.9380000000001</v>
       </c>
-      <c r="B2222" s="1">
-        <v>0.10137731481481481</v>
+      <c r="B2222" s="4">
+        <v>0.66</v>
       </c>
       <c r="C2222" s="2">
         <v>51.160159999999998</v>
@@ -24850,8 +24856,8 @@
       <c r="A2223" s="2">
         <v>1401.8130000000001</v>
       </c>
-      <c r="B2223" s="1">
-        <v>0.10140046296296296</v>
+      <c r="B2223" s="4">
+        <v>0.67</v>
       </c>
       <c r="C2223" s="2">
         <v>51.160159999999998</v>
@@ -24861,8 +24867,8 @@
       <c r="A2224" s="2">
         <v>1404.0630000000001</v>
       </c>
-      <c r="B2224" s="1">
-        <v>0.10141203703703704</v>
+      <c r="B2224" s="4">
+        <v>0.68</v>
       </c>
       <c r="C2224" s="2">
         <v>51.160159999999998</v>
@@ -24872,8 +24878,8 @@
       <c r="A2225" s="2">
         <v>1409.375</v>
       </c>
-      <c r="B2225" s="1">
-        <v>0.10142361111111112</v>
+      <c r="B2225" s="4">
+        <v>0.69</v>
       </c>
       <c r="C2225" s="2">
         <v>51.160159999999998</v>
@@ -24883,8 +24889,8 @@
       <c r="A2226" s="2">
         <v>1405.8130000000001</v>
       </c>
-      <c r="B2226" s="1">
-        <v>0.10146990740740741</v>
+      <c r="B2226" s="4">
+        <v>0.7</v>
       </c>
       <c r="C2226" s="2">
         <v>51.160159999999998</v>
@@ -24894,8 +24900,8 @@
       <c r="A2227" s="2">
         <v>1411.3130000000001</v>
       </c>
-      <c r="B2227" s="1">
-        <v>0.10149305555555556</v>
+      <c r="B2227" s="4">
+        <v>0.71</v>
       </c>
       <c r="C2227" s="2">
         <v>51.160159999999998</v>
@@ -24905,8 +24911,8 @@
       <c r="A2228" s="2">
         <v>1408.4380000000001</v>
       </c>
-      <c r="B2228" s="1">
-        <v>0.10157407407407408</v>
+      <c r="B2228" s="4">
+        <v>0.72</v>
       </c>
       <c r="C2228" s="2">
         <v>51.160159999999998</v>
@@ -24916,8 +24922,8 @@
       <c r="A2229" s="2">
         <v>1405.25</v>
       </c>
-      <c r="B2229" s="1">
-        <v>0.10158564814814815</v>
+      <c r="B2229" s="4">
+        <v>0.73</v>
       </c>
       <c r="C2229" s="2">
         <v>51.160159999999998</v>
@@ -24927,8 +24933,8 @@
       <c r="A2230" s="2">
         <v>1411.4380000000001</v>
       </c>
-      <c r="B2230" s="1">
-        <v>0.10162037037037037</v>
+      <c r="B2230" s="4">
+        <v>0.74</v>
       </c>
       <c r="C2230" s="2">
         <v>51.160159999999998</v>
@@ -24938,8 +24944,8 @@
       <c r="A2231" s="2">
         <v>1415.3130000000001</v>
       </c>
-      <c r="B2231" s="1">
-        <v>0.10163194444444444</v>
+      <c r="B2231" s="4">
+        <v>0.75</v>
       </c>
       <c r="C2231" s="2">
         <v>51.160159999999998</v>
@@ -24949,8 +24955,8 @@
       <c r="A2232" s="2">
         <v>1412.125</v>
       </c>
-      <c r="B2232" s="1">
-        <v>0.10167824074074074</v>
+      <c r="B2232" s="4">
+        <v>0.76</v>
       </c>
       <c r="C2232" s="2">
         <v>51.160159999999998</v>
@@ -24960,8 +24966,8 @@
       <c r="A2233" s="2">
         <v>1407.1880000000001</v>
       </c>
-      <c r="B2233" s="1">
-        <v>0.10168981481481482</v>
+      <c r="B2233" s="4">
+        <v>0.77</v>
       </c>
       <c r="C2233" s="2">
         <v>51.160159999999998</v>
@@ -24971,8 +24977,8 @@
       <c r="A2234" s="2">
         <v>1403.875</v>
       </c>
-      <c r="B2234" s="1">
-        <v>0.10170138888888888</v>
+      <c r="B2234" s="4">
+        <v>0.78</v>
       </c>
       <c r="C2234" s="2">
         <v>51.160159999999998</v>
@@ -24982,8 +24988,8 @@
       <c r="A2235" s="2">
         <v>1401.125</v>
       </c>
-      <c r="B2235" s="1">
-        <v>0.10171296296296296</v>
+      <c r="B2235" s="4">
+        <v>0.79</v>
       </c>
       <c r="C2235" s="2">
         <v>51.160159999999998</v>
@@ -24993,8 +24999,8 @@
       <c r="A2236" s="2">
         <v>1405.125</v>
       </c>
-      <c r="B2236" s="1">
-        <v>0.10174768518518519</v>
+      <c r="B2236" s="4">
+        <v>0.8</v>
       </c>
       <c r="C2236" s="2">
         <v>51.160159999999998</v>
@@ -25004,8 +25010,8 @@
       <c r="A2237" s="2">
         <v>1407.8130000000001</v>
       </c>
-      <c r="B2237" s="1">
-        <v>0.10175925925925926</v>
+      <c r="B2237" s="4">
+        <v>0.81</v>
       </c>
       <c r="C2237" s="2">
         <v>51.160159999999998</v>
@@ -25015,8 +25021,8 @@
       <c r="A2238" s="2">
         <v>1411.5630000000001</v>
       </c>
-      <c r="B2238" s="1">
-        <v>0.1017824074074074</v>
+      <c r="B2238" s="4">
+        <v>0.82</v>
       </c>
       <c r="C2238" s="2">
         <v>51.160159999999998</v>
@@ -25026,8 +25032,8 @@
       <c r="A2239" s="2">
         <v>1413.9380000000001</v>
       </c>
-      <c r="B2239" s="1">
-        <v>0.10179398148148149</v>
+      <c r="B2239" s="4">
+        <v>0.83</v>
       </c>
       <c r="C2239" s="2">
         <v>51.160159999999998</v>
@@ -25037,8 +25043,8 @@
       <c r="A2240" s="2">
         <v>1417.5630000000001</v>
       </c>
-      <c r="B2240" s="1">
-        <v>0.10180555555555555</v>
+      <c r="B2240" s="4">
+        <v>0.84</v>
       </c>
       <c r="C2240" s="2">
         <v>51.160159999999998</v>
@@ -25048,8 +25054,8 @@
       <c r="A2241" s="2">
         <v>1421.5630000000001</v>
       </c>
-      <c r="B2241" s="1">
-        <v>0.10184027777777778</v>
+      <c r="B2241" s="4">
+        <v>0.85</v>
       </c>
       <c r="C2241" s="2">
         <v>51.160159999999998</v>
@@ -25059,8 +25065,8 @@
       <c r="A2242" s="2">
         <v>1425.3130000000001</v>
       </c>
-      <c r="B2242" s="1">
-        <v>0.10185185185185185</v>
+      <c r="B2242" s="4">
+        <v>0.86</v>
       </c>
       <c r="C2242" s="2">
         <v>51.160159999999998</v>
@@ -25070,8 +25076,8 @@
       <c r="A2243" s="2">
         <v>1423</v>
       </c>
-      <c r="B2243" s="1">
-        <v>0.10187499999999999</v>
+      <c r="B2243" s="4">
+        <v>0.87</v>
       </c>
       <c r="C2243" s="2">
         <v>51.160159999999998</v>
@@ -25081,8 +25087,8 @@
       <c r="A2244" s="2">
         <v>1426.5</v>
       </c>
-      <c r="B2244" s="1">
-        <v>0.10190972222222222</v>
+      <c r="B2244" s="4">
+        <v>0.88</v>
       </c>
       <c r="C2244" s="2">
         <v>51.160159999999998</v>
